--- a/public/business-plans/finance.xlsx
+++ b/public/business-plans/finance.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,10 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
@@ -66,12 +70,17 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,19 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +570,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Финансовый сектор и страхование». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
+          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Финансовый сектор и страхование». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Абзацы, отмеченные как «ПРИМЕР», — иллюстрация формата ответа, а не факты о реальной компании; замените их своими данными. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -592,31 +604,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): МФО «QulayQarz» выдаёт микрозаймы предпринимателям на пополнение оборотных средств через мобильное приложение со скоринг-моделью на основе транзакционных данных. Требуемый капитал — 1,2 млрд сум (включая фонд выдачи первых займов); окупаемость — около 20 месяцев при среднем размере займа и плановом уровне невозврата.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] В 5-8 предложениях: суть проекта, какую проблему решает, для кого, требуемая сумма инвестиций и на что она пойдёт, ожидаемый результат (выручка/прибыль/срок окупаемости).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Описание компании / проекта</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Организационно-правовая форма (ИП/ООО/фермерское хозяйство), команда, текущий статус проекта (идея / MVP / действующий бизнес), уникальное торговое предложение.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -628,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -641,68 +661,84 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="59" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>•  В Узбекистане активно развивается финтех — Центральный банк регулирует и поддерживает цифровизацию платежей.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>•  В Узбекистане активно развивается финтех-экосистема на фоне роста цифровых платежей — Центральный банк регулирует и поддерживает цифровизацию платёжной инфраструктуры, включая развитие национальных платёжных систем (Uzcard, Humo) и подключение к ним новых сервисов (uzdaily.uz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="74" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>•  Растёт проникновение мобильного банкинга и безналичных платежей среди населения и бизнеса.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>•  По оценке Азиатского банка развития, перед Узбекистаном стоит задача не только нарастить объём цифровых платежей, но и превратить цифровые финансы в реальные накопления населения и доступ к капиталу для МСБ — то есть развитие идёт не только в сторону платежей, но и сберегательных/кредитных продуктов (uzdaily.uz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>•  Растущий спрос МСБ на микрофинансирование и лизинг, особенно в регионах с ограниченным доступом к банковским услугам.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>•  Растёт проникновение мобильного банкинга и безналичных платежей среди населения и бизнеса в крупных городах — но в регионах доступ к цифровым финансовым услугам и финансовая грамотность остаются ниже, что создаёт как барьер, так и нишу для локализованных продуктов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>•  [Впишите] Конкретную нишу (платежи/кредитование/лизинг/страхование), требования лицензирования ЦБ РУз для неё.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Конкуренты</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+          <t>•  Растущий спрос МСБ на микрофинансирование и лизинг, особенно в регионах с ограниченным доступом к банковским услугам — при этом деятельность МФО и платёжных сервисов подлежит лицензированию и надзору ЦБ РУз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="74" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>•  Для сравнения: Казахстан и Россия имеют более зрелые финтех-рынки с крупными игроками (Kaspi.kz, Тинькофф) — узбекский рынок ещё формируется, что даёт возможность занять нишу быстрее, но также означает менее отработанную нормативную базу и более высокую регуляторную неопределённость.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>•  [Впишите] Конкретную нишу (платежи/кредитование/лизинг/страхование), требования лицензирования ЦБ РУз для неё и данные по объёму сегмента — уточняйте на сайте cbu.uz.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Целевая аудитория</t>
+          <t>Конкуренты</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Целевая аудитория</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
@@ -716,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -729,117 +765,183 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="59" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Продвижение — партнёрство с 2-3 маркетплейсами и поставщиками для встроенного кредитования (embedded finance) их продавцов, таргетированная реклама в соцсетях для предпринимателей, реферальная программа для существующих клиентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Ценообразование, каналы продвижения и продаж, план привлечения первых клиентов.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Операционный план</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="59" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цикл: заявка через приложение → скоринг и проверка → одобрение → выдача займа на карту → автоматическое списание платежей по графику → работа с просрочкой. Требуется лицензия ЦБ РУз на деятельность МФО и внедрение AML/KYC-процедур.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Процесс производства/оказания услуги, ключевые поставщики, оборудование, необходимые лицензии и разрешения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Организационный план</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Организационный план</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Директор, риск-менеджер/скоринг-аналитик, комплаенс-офицер, 2 менеджера по работе с клиентами, разработчик приложения на аутсорсе. Форма — ООО с лицензией МФО от ЦБ РУз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Риски и меры по их снижению (примеры для отрасли)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Меры снижения</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Кредитный риск (невозврат)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Скоринг заёмщиков, диверсификация портфеля</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Регуляторные изменения</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Постоянный мониторинг требований ЦБ РУз</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Киберугрозы</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Аудит безопасности, страхование киберрисков</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Кредитный риск (невозврат займов)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Скоринг заёмщиков на основе данных, диверсификация портфеля, лимиты на одного заёмщика</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Регуляторные изменения со стороны ЦБ РУз</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Постоянный мониторинг требований, резерв времени и бюджета на комплаенс</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Киберугрозы и утечка финансовых данных клиентов</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Аудит информационной безопасности, страхование киберрисков, шифрование данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Валютные риски при работе с иностранными инвесторами/платформами</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Хеджирование, расчёты преимущественно в национальной валюте</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Низкая финансовая грамотность части целевой аудитории</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Простой и понятный интерфейс, обучающий контент, поддержка на местном языке</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="59" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Репутационный риск при агрессивном взыскании задолженности</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Прозрачная и этичная политика взыскания, соответствие требованиям ЦБ РУз по защите прав потребителей</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Дополните таблицу своими рисками, специфичными для вашего проекта и региона.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="21">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -856,309 +958,313 @@
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Сумма, сум</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Добавляйте свои строки при необходимости.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Лицензирование деятельности</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>требования ЦБ РУз по выбранному виду деятельности</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>IT-платформа / приложение</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Капитал для выдачи первых займов</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>если МФО</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Комплаенс и AML-системы</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Комплаенс и AML/KYC-системы</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Офис и оборудование</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Итого: стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="16">
         <f>SUM(B7:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="16" t="n"/>
+      <c r="C12" s="17" t="n"/>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Процентный доход по займам/лизингу</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Комиссии за транзакции/обслуживание</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Партнёрские комиссии</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
+      <c r="B16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Партнёрские комиссии (embedded finance)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>за встроенные финансовые продукты у партнёров</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="16">
         <f>SUM(B15:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="16" t="n"/>
+      <c r="C18" s="17" t="n"/>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>ФОТ (включая комплаенс и риск-менеджмент)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="B21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>IT-инфраструктура и кибербезопасность</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Резервы на возможные потери по займам</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Маркетинг и привлечение клиентов</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Лицензионные и регуляторные сборы</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="16">
         <f>SUM(B21:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Ежемесячная прибыль</t>
         </is>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <f>B18-B26</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Срок выхода на окупаемость, мес.</t>
         </is>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="14">
         <f>IFERROR(B4/B28,"—")</f>
         <v/>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="14">
         <f> Начальные инвестиции / Ежемесячная прибыль</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Рентабельность продаж, %</t>
         </is>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="18">
         <f>IFERROR(B28/B18*100,"—")</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="14">
         <f> Ежемесячная прибыль / Выручка × 100%</f>
         <v/>
       </c>
     </row>
     <row r="32"/>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта.</t>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
         </is>
       </c>
     </row>

--- a/public/business-plans/finance.xlsx
+++ b/public/business-plans/finance.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +126,9 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ФИНАНСОВЫЙ ПЛАН: ФИНАНСОВЫЙ СЕКТОР И СТРАХОВАНИЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>ФИНАНСОВЫЙ ПЛАН: ФИНАНСОВЫЙ СЕКТОР И СТРАХОВАНИЕ — ПРИМЕР РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Финансовый сектор и страхование» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — только расчётная часть с рабочими формулами.</t>
+          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Финансовый сектор и страхование» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — расчётная часть с рабочими формулами, уже заполненная цифрами ПРИМЕРА (иллюстративная компания из резюме бизнес-плана, не реальный заёмщик) — чтобы показать порядок величины и логику расчёта. Перед подачей в банк или инвестору замените суммы на данные своего проекта.</t>
         </is>
       </c>
     </row>
@@ -527,10 +534,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
+          <t>Столбец «Сумма, сум» уже заполнен примером расчёта для иллюстративной компании из этого бизнес-плана — на основе рыночных ориентиров 2025-2026 года (там, где источник известен — со ссылкой в комментарии) или экспертной оценки порядка величины (это тоже отмечено). Итоги, прибыль, срок окупаемости и рентабельность ниже пересчитаются автоматически (это формулы). Замените суммы в столбце B на данные вашего собственного проекта — тогда пересчитается всё.</t>
         </is>
       </c>
     </row>
@@ -541,8 +548,9 @@
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
+      <c r="B7" s="6">
+        <f>B15</f>
+        <v/>
       </c>
     </row>
     <row r="8"/>
@@ -555,68 +563,80 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Лицензирование деятельности</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>требования ЦБ РУз по выбранному виду деятельности</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+          <t>требования ЦБ РУз по выбранному виду деятельности — Пример: оценка: юр. сопровождение регистрации МКО, госпошлины, обязательные публикации</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>IT-платформа / приложение</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+        <v>190000000</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка стоимости разработки мобильного приложения со скоринговой моделью и бэкендом (MVP, аутсорс)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Капитал для выдачи первых займов</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
+        <v>850000000</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>если МФО</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
+          <t>если МФО — Пример: оценка: остаток бюджета 1,2 млрд сум после прочих статей — формирует стартовый кредитный портфель</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Комплаенс и AML/KYC-системы</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
+        <v>50000000</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: системы идентификации клиентов, скоринговые интеграции, AML-мониторинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Офис и оборудование</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr"/>
+        <v>92000000</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: аренда/ремонт небольшого офиса, мебель и техника для команды ~5 человек</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -640,40 +660,48 @@
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
     </row>
-    <row r="18" ht="21" customHeight="1">
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Процентный доход по займам/лизингу</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="21" customHeight="1">
+        <v>35500000</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Пример: портфель ~850 млн × ~50% годовых / 12 — ставка ограничена потолком ЦБ РУз (совокупная переплата ≤50%/год с апр. 2025, Spot.uz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Комиссии за транзакции/обслуживание</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+        <v>8500000</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка дохода от комиссий за обслуживание/переводы в рамках общего лимита переплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Партнёрские комиссии (embedded finance)</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0</v>
+        <v>16000000</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>за встроенные финансовые продукты у партнёров</t>
+          <t>за встроенные финансовые продукты у партнёров — Пример: оценка дохода от партнёрств с маркетплейсами за встроенное кредитование продавцов</t>
         </is>
       </c>
     </row>
@@ -699,60 +727,80 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
     </row>
-    <row r="24" ht="21" customHeight="1">
+    <row r="24" ht="51" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>ФОТ (включая комплаенс и риск-менеджмент)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr"/>
-    </row>
-    <row r="25" ht="21" customHeight="1">
+        <v>30000000</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Пример: компактная стартовая команда (директор, риск-менеджер, комплаенс, 2 менеджера) — оценка по уровню малых финтех-компаний Ташкента</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>IT-инфраструктура и кибербезопасность</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26" ht="21" customHeight="1">
+        <v>6000000</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: разработчик на аутсорсе, облачный хостинг, защита персональных данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Резервы на возможные потери по займам</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
+        <v>3500000</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Пример: расчёт: ~5% годовых от портфеля 850 млн / 12 — консервативная норма резервирования</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Маркетинг и привлечение клиентов</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <v>3000000</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка расходов на привлечение первых заёмщиков через цифровые каналы</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Лицензионные и регуляторные сборы</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr"/>
+        <v>2000000</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка расходов на отчётность перед ЦБ, аудит, регуляторные сборы</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -789,9 +837,10 @@
         <f>IFERROR(B7/B31,"—")</f>
         <v/>
       </c>
-      <c r="C33" s="9">
-        <f> Начальные инвестиции / Ежемесячная прибыль</f>
-        <v/>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Начальные инвестиции ÷ Ежемесячная прибыль</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -804,22 +853,32 @@
         <f>IFERROR(B31/B21*100,"—")</f>
         <v/>
       </c>
-      <c r="C34" s="9">
-        <f> Ежемесячная прибыль / Выручка × 100%</f>
-        <v/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Ежемесячная прибыль ÷ Выручка × 100%</t>
+        </is>
       </c>
     </row>
     <row r="35"/>
-    <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
+    <row r="36" ht="110" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Как считался этот пример: ВАЖНО про срок окупаемости: 850 млн сум 'фонда выдачи займов' — это оборотный актив (портфель), а не безвозвратные вложения, поэтому делить весь 1,2 млрд на месячную прибыль (≈15,5 млн) некорректно — так выйдет ≈77 мес. Если считать окупаемость только по невозвратным разовым вложениям (лицензирование + IT-платформа + комплаенс + офис = 350 млн), срок ≈22,6 мес. — близко к заявленным ~20 мес. Это методологически корректный способ считать окупаемость для кредитного бизнеса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="55" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Это пример расчёта для иллюстративной компании, а не готовая заявка на кредит и не проверенные рыночные данные о реальном бизнесе. Суммы в столбце B — рабочие формулы: замените их на цифры вашего проекта, и итоги, прибыль, срок окупаемости и рентабельность пересчитаются автоматически. Там, где в комментарии указан источник — это ориентир на 2025-2026 год, проверяйте актуальность перед подачей документов в банк; где указана «экспертная оценка» — это иллюстрация порядка величины, а не факт.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
